--- a/static/data/exports/Retro_KL_GE_2024.xlsx
+++ b/static/data/exports/Retro_KL_GE_2024.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_KL_GE_2024.xlsx
+++ b/static/data/exports/Retro_KL_GE_2024.xlsx
@@ -3445,11 +3445,11 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1700441</v>
+        <v>1700442</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Balakrishnan N</t>
+          <t>Manoharan K</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3464,7 +3464,7 @@
         <v>85</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0532014771233648</v>
+        <v>0.05</v>
       </c>
       <c r="G49" t="n">
         <v>8</v>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Balakrishnan N</t>
+          <t>Manoharan K</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3507,11 +3507,11 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1700442</v>
+        <v>1700441</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Manoharan K</t>
+          <t>Balakrishnan N</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3526,7 +3526,7 @@
         <v>85</v>
       </c>
       <c r="F50" t="n">
-        <v>0.05</v>
+        <v>0.0532014771233648</v>
       </c>
       <c r="G50" t="n">
         <v>8</v>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Manoharan K</t>
+          <t>Balakrishnan N</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -17023,11 +17023,11 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>1701807</v>
+        <v>1701808</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Muralidharan</t>
+          <t>Sylaja P</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>Muralidharan</t>
+          <t>Sylaja P</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -17085,11 +17085,11 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>1701808</v>
+        <v>1701807</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Sylaja P</t>
+          <t>Muralidharan</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -17122,7 +17122,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>Sylaja P</t>
+          <t>Muralidharan</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -35375,11 +35375,11 @@
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>1703851</v>
+        <v>1703850</v>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Sidheek Iruppassery</t>
+          <t>Rajesh M Son Of Mani C</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -35394,7 +35394,7 @@
         <v>117</v>
       </c>
       <c r="F564" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0748474264000307</v>
       </c>
       <c r="G564" t="n">
         <v>9</v>
@@ -35412,7 +35412,7 @@
       </c>
       <c r="K564" t="inlineStr">
         <is>
-          <t>Sidheek Iruppassery</t>
+          <t>Rajesh M Son Of Mani C</t>
         </is>
       </c>
       <c r="L564" t="inlineStr">
@@ -35437,11 +35437,11 @@
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>1703850</v>
+        <v>1703851</v>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Rajesh M Son Of Mani C</t>
+          <t>Sidheek Iruppassery</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -35456,7 +35456,7 @@
         <v>117</v>
       </c>
       <c r="F565" t="n">
-        <v>0.0748474264000307</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G565" t="n">
         <v>9</v>
@@ -35474,7 +35474,7 @@
       </c>
       <c r="K565" t="inlineStr">
         <is>
-          <t>Rajesh M Son Of Mani C</t>
+          <t>Sidheek Iruppassery</t>
         </is>
       </c>
       <c r="L565" t="inlineStr">
@@ -42505,26 +42505,26 @@
     </row>
     <row r="679">
       <c r="A679" t="n">
-        <v>1704727</v>
+        <v>1704726</v>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Prathapan</t>
+          <t>Divakaran Pallath</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NWLBRP</t>
         </is>
       </c>
       <c r="D679" t="n">
-        <v>19702</v>
+        <v>19725</v>
       </c>
       <c r="E679" t="n">
         <v>111</v>
       </c>
       <c r="F679" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07054740976604949</v>
       </c>
       <c r="G679" t="n">
         <v>7</v>
@@ -42542,12 +42542,12 @@
       </c>
       <c r="K679" t="inlineStr">
         <is>
-          <t>Prathapan</t>
+          <t>Divakaran Pallath</t>
         </is>
       </c>
       <c r="L679" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NWLBRP</t>
         </is>
       </c>
       <c r="Q679" t="b">
@@ -42567,26 +42567,26 @@
     </row>
     <row r="680">
       <c r="A680" t="n">
-        <v>1704726</v>
+        <v>1704727</v>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Divakaran Pallath</t>
+          <t>Prathapan</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>NWLBRP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D680" t="n">
-        <v>19725</v>
+        <v>19702</v>
       </c>
       <c r="E680" t="n">
         <v>111</v>
       </c>
       <c r="F680" t="n">
-        <v>0.07054740976604949</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G680" t="n">
         <v>7</v>
@@ -42604,12 +42604,12 @@
       </c>
       <c r="K680" t="inlineStr">
         <is>
-          <t>Divakaran Pallath</t>
+          <t>Prathapan</t>
         </is>
       </c>
       <c r="L680" t="inlineStr">
         <is>
-          <t>NWLBRP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q680" t="b">
@@ -45791,26 +45791,26 @@
     </row>
     <row r="732">
       <c r="A732" t="n">
-        <v>1705073</v>
+        <v>1705074</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Divakaran Pallath</t>
+          <t>M S Jafarghan</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>NWLBRP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D732" t="n">
-        <v>19725</v>
+        <v>19702</v>
       </c>
       <c r="E732" t="n">
         <v>126</v>
       </c>
       <c r="F732" t="n">
-        <v>0.0800808435182183</v>
+        <v>0.08</v>
       </c>
       <c r="G732" t="n">
         <v>8</v>
@@ -45828,12 +45828,12 @@
       </c>
       <c r="K732" t="inlineStr">
         <is>
-          <t>Divakaran Pallath</t>
+          <t>M S Jafarghan</t>
         </is>
       </c>
       <c r="L732" t="inlineStr">
         <is>
-          <t>NWLBRP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q732" t="b">
@@ -45853,26 +45853,26 @@
     </row>
     <row r="733">
       <c r="A733" t="n">
-        <v>1705074</v>
+        <v>1705073</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>M S Jafarghan</t>
+          <t>Divakaran Pallath</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NWLBRP</t>
         </is>
       </c>
       <c r="D733" t="n">
-        <v>19702</v>
+        <v>19725</v>
       </c>
       <c r="E733" t="n">
         <v>126</v>
       </c>
       <c r="F733" t="n">
-        <v>0.08</v>
+        <v>0.0800808435182183</v>
       </c>
       <c r="G733" t="n">
         <v>8</v>
@@ -45890,12 +45890,12 @@
       </c>
       <c r="K733" t="inlineStr">
         <is>
-          <t>M S Jafarghan</t>
+          <t>Divakaran Pallath</t>
         </is>
       </c>
       <c r="L733" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NWLBRP</t>
         </is>
       </c>
       <c r="Q733" t="b">
@@ -68793,26 +68793,26 @@
     </row>
     <row r="1103">
       <c r="A1103" t="n">
-        <v>1707537</v>
+        <v>1707538</v>
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>Vayalar Rajeevan</t>
+          <t>Adv.K.M Shajahan</t>
         </is>
       </c>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>BHUDRP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D1103" t="n">
-        <v>19740</v>
+        <v>19702</v>
       </c>
       <c r="E1103" t="n">
         <v>85</v>
       </c>
       <c r="F1103" t="n">
-        <v>0.0563851169825338</v>
+        <v>0.06</v>
       </c>
       <c r="G1103" t="n">
         <v>7</v>
@@ -68830,12 +68830,12 @@
       </c>
       <c r="K1103" t="inlineStr">
         <is>
-          <t>Vayalar Rajeevan</t>
+          <t>Adv.K.M Shajahan</t>
         </is>
       </c>
       <c r="L1103" t="inlineStr">
         <is>
-          <t>BHUDRP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q1103" t="b">
@@ -68855,26 +68855,26 @@
     </row>
     <row r="1104">
       <c r="A1104" t="n">
-        <v>1707538</v>
+        <v>1707537</v>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>Adv.K.M Shajahan</t>
+          <t>Vayalar Rajeevan</t>
         </is>
       </c>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BHUDRP</t>
         </is>
       </c>
       <c r="D1104" t="n">
-        <v>19702</v>
+        <v>19740</v>
       </c>
       <c r="E1104" t="n">
         <v>85</v>
       </c>
       <c r="F1104" t="n">
-        <v>0.06</v>
+        <v>0.0563851169825338</v>
       </c>
       <c r="G1104" t="n">
         <v>7</v>
@@ -68892,12 +68892,12 @@
       </c>
       <c r="K1104" t="inlineStr">
         <is>
-          <t>Adv.K.M Shajahan</t>
+          <t>Vayalar Rajeevan</t>
         </is>
       </c>
       <c r="L1104" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BHUDRP</t>
         </is>
       </c>
       <c r="Q1104" t="b">
@@ -83177,20 +83177,20 @@
     </row>
     <row r="1335">
       <c r="A1335" t="n">
-        <v>1708969</v>
+        <v>1708968</v>
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>Bro Noushad Sheriff J</t>
+          <t>Pradeep Kottarakkara</t>
         </is>
       </c>
       <c r="C1335" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BJKP</t>
         </is>
       </c>
       <c r="D1335" t="n">
-        <v>19702</v>
+        <v>19723</v>
       </c>
       <c r="E1335" t="n">
         <v>63</v>
@@ -83214,12 +83214,12 @@
       </c>
       <c r="K1335" t="inlineStr">
         <is>
-          <t>Bro Noushad Sheriff J</t>
+          <t>Pradeep Kottarakkara</t>
         </is>
       </c>
       <c r="L1335" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BJKP</t>
         </is>
       </c>
       <c r="Q1335" t="b">
@@ -83239,20 +83239,20 @@
     </row>
     <row r="1336">
       <c r="A1336" t="n">
-        <v>1708968</v>
+        <v>1708969</v>
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>Pradeep Kottarakkara</t>
+          <t>Bro Noushad Sheriff J</t>
         </is>
       </c>
       <c r="C1336" t="inlineStr">
         <is>
-          <t>BJKP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D1336" t="n">
-        <v>19723</v>
+        <v>19702</v>
       </c>
       <c r="E1336" t="n">
         <v>63</v>
@@ -83276,12 +83276,12 @@
       </c>
       <c r="K1336" t="inlineStr">
         <is>
-          <t>Pradeep Kottarakkara</t>
+          <t>Bro Noushad Sheriff J</t>
         </is>
       </c>
       <c r="L1336" t="inlineStr">
         <is>
-          <t>BJKP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q1336" t="b">
